--- a/evaluation/fairness_measure_based/OLS_Regression_Feature_Analysis_Generalized_Cross_Entropy.xlsx
+++ b/evaluation/fairness_measure_based/OLS_Regression_Feature_Analysis_Generalized_Cross_Entropy.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,314 +441,784 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>P-Value</t>
+          <t>t</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Significance</t>
+          <t>P-Value (raw)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-Value (Bonferroni)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Reject (Bonf@0.05)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Partial_R2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cohen_f2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Significance (raw)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Significance (bonf)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mean Rating</t>
+          <t>Difference between Sensitive Attribute Percentage</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2360528449829241</v>
+        <v>-0.3092575461653046</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02415188245974485</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>*</t>
+        <v>-12.9060854497035</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.023110381620716e-35</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.105084283956558e-33</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1591556345734157</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7201145713315232</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>***</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dataset_BX</t>
+          <t>Rating per User</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1329831723817231</v>
+        <v>-0.05696940037691417</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00438259541236635</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>**</t>
+        <v>-5.265478926591658</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.7583991295098e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.868478084921559e-06</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.03054367802000193</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1381977311906974</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>***</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Number of Ratings</t>
+          <t>Mean Rating</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08336578853006907</v>
+        <v>0.250200126264003</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07478194442257743</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>4.064046602139062</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.254208400387762e-05</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.001155925848085308</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01842294620222213</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.08335634514376708</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gini Item</t>
+          <t>Number of Items</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0463738559195384</v>
+        <v>-0.06424997021431578</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2555849902778649</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>-4.001950051708579</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.811121477439411e-05</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.001498446725036671</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.01787424698967948</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.08087370417859388</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Skewness of Popularity Bias</t>
+          <t>Number of Ratings</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0151349800269134</v>
+        <v>0.08754466746202005</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4201411027700777</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>3.171267885473775</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.001570312817251052</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.03454688197952314</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.01129920969036101</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.05112433225734137</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>Standart Deviation of Rating</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01274445868200105</v>
+        <v>-0.0951632651057186</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7093791665272037</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>-2.915178230030496</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.003645035432281534</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.08019077951019374</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.009564750383985458</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.04327660871773616</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sensitive Feature_Gender</t>
+          <t>Number of Users</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008165155773005653</v>
+        <v>-0.05157000771168506</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6305090640740842</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>-2.760739665037677</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.005887034441322059</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1295147577090853</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.008586635094441736</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.03885103450334867</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sensitive Feature_Age</t>
+          <t>Rating per Item</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004579302908996698</v>
+        <v>-0.04230247158110299</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8034714322620029</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>-2.151144662460126</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.03173641819717728</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.6982012003379001</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005230929130888667</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0236678286562194</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shape</t>
+          <t>Gini Item</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0009113497745449461</v>
+        <v>0.0471443433343321</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9760758973257406</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>1.947779579399317</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.05175901132962343</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.004292681274195144</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01942263837479136</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hit@5</t>
+          <t>Skewness of Popularity Bias</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.005192426630962078</v>
+        <v>0.01794792370698626</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4967034760916094</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>1.602447095552271</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1094156355821101</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.002909506314735658</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01316433375568466</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Skewness of Long Tail Items</t>
+          <t>Density</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.01068228251591537</v>
+        <v>-0.02587744321369403</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5628447091979043</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>-1.12333146220861</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2616031049479344</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.001431893982738823</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.006478738401790695</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gini User</t>
+          <t>Skewness of Long Tail Items</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.01847222354653513</v>
+        <v>-0.01091766037303271</v>
       </c>
       <c r="C13" t="n">
-        <v>0.495926990296735</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>-1.001017611337383</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3170934622627286</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.001137382454260206</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.005146193414294567</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Density</t>
+          <t>Gini User</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.03488645650933091</v>
+        <v>-0.01597581784219029</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3752264048132876</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>-0.995413633385684</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3198087557738531</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.001124697610015307</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.005088799648749878</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rating per Item</t>
+          <t>Dataset_BX</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.03937107328666113</v>
+        <v>27045962939.70552</v>
       </c>
       <c r="C15" t="n">
-        <v>0.23709638133572</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>0.6482066063654847</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5170204219590593</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0004772400928464207</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.00215931748695827</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Number of Users</t>
+          <t>Model Name_PFCN_MLP</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.04554591179601011</v>
+        <v>18135639251.51714</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1487926932791002</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>0.6482066063622688</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.517020421961138</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0004772400928416876</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.002159317486936854</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rating per User</t>
+          <t>Model Name_NFCF</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.05249263412860186</v>
+        <v>18135639251.51597</v>
       </c>
       <c r="C17" t="n">
-        <v>0.004457213217096669</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
+        <v>0.6482066063622275</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5170204219611648</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0004772400928416268</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.002159317486936579</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Number of Items</t>
+          <t>const</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06046848205830307</v>
+        <v>44614906087.66083</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02662119664283453</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+        <v>0.6482066063621955</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.5170204219611854</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0004772400928415798</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.002159317486936366</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Standart Deviation of Rating</t>
+          <t>Sensitive Feature_Age</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.09482000900521763</v>
+        <v>-89796508278.73657</v>
       </c>
       <c r="C19" t="n">
-        <v>0.08705961616525311</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>-0.6482066063621494</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.5170204219612151</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.000477240092841512</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.00215931748693606</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dataset_ml1m</t>
+          <t>Sensitive Feature_Gender</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1202387136997213</v>
+        <v>-89796508278.72891</v>
       </c>
       <c r="C20" t="n">
-        <v>0.07106346003001217</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>-0.6482066063620936</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.5170204219612513</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0004772400928414297</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.002159317486935688</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Difference between Sensitive Attribute Percentage</t>
+          <t>Model Name_FOCF</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.3161887903886004</v>
+        <v>18135639251.51142</v>
       </c>
       <c r="C21" t="n">
-        <v>1.140372843993806e-13</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>0.6482066063620614</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.517020421961272</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0004772400928413825</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.002159317486935474</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>27045962939.43118</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.6482066063588873</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.5170204219633237</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0004772400928367108</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.002159317486914336</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.004382437310932673</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.6055755152665687</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.5449528104382346</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0004165556189814534</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.001884744902702121</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Shape</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.002556938900123715</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.1423552413910953</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.8868319996732572</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.302789555781118e-05</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0001041918696923732</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
